--- a/artfynd/A 18188-2026 artfynd.xlsx
+++ b/artfynd/A 18188-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99169974</v>
+        <v>120868982</v>
       </c>
       <c r="B2" t="n">
-        <v>104127</v>
+        <v>57132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,57 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lingbo, Rännkolsberget söder foten, nedom vägen, Gstr</t>
+          <t>N om Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588350</v>
+        <v>588752</v>
       </c>
       <c r="R2" t="n">
-        <v>6765592</v>
+        <v>6765074</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +760,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-08-10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-08-10</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Calluna AB, EEN0082</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,32 +782,18 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>skog, Blandskog, ungskog i sydsluttning, gran, gråal i glänta</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 163093N</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Gästriklands flora (2016)</t>
-        </is>
-      </c>
+          <t>Arvid Löf</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
